--- a/Manual Matching.xlsx
+++ b/Manual Matching.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\LN2PEPF0000C387\EXCELCNV\4a5afe72-f96d-485f-9a48-7f676b45cfc2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hm1425_ic_ac_uk/Documents/STEMM/Term 1/UCAS mentoring testing/Matching Algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{CABD2E83-5C2C-417D-9B32-38DD2491E369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F9A7F6D-E07F-4883-BC3E-E92DB39586AF}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{CABD2E83-5C2C-417D-9B32-38DD2491E369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C65961-452F-4283-B1C3-6F09711DF662}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{08F4247C-0A8B-4665-98F2-8C71D6D769FC}"/>
+    <workbookView xWindow="1800" yWindow="1410" windowWidth="27000" windowHeight="14790" xr2:uid="{08F4247C-0A8B-4665-98F2-8C71D6D769FC}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,39 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E59F53BC-32D6-4656-80B0-48EDCC40972B}</author>
+    <author>tc={350E727E-3F65-4A3F-8B56-638D0C8379BF}</author>
+  </authors>
+  <commentList>
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{E59F53BC-32D6-4656-80B0-48EDCC40972B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    whos this?
+cant see them on mentee list
+Reply:
+    Some girl called Insia Zafar. Applying for materials. Shes on the mentee list</t>
+      </text>
+    </comment>
+    <comment ref="A50" authorId="1" shapeId="0" xr:uid="{350E727E-3F65-4A3F-8B56-638D0C8379BF}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    manually added this sister (she didnt fill the form)
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="121">
   <si>
     <t>Mentor_Email</t>
   </si>
@@ -65,9 +96,6 @@
     <t>naziat.06@gmail.com</t>
   </si>
   <si>
-    <t>yyi25@ic.ac.uk 06yusufibrahim@gmail.com</t>
-  </si>
-  <si>
     <t>77muhammedhamza@gmail.com</t>
   </si>
   <si>
@@ -390,13 +418,25 @@
   </si>
   <si>
     <t>yuslam619@gmail.com</t>
+  </si>
+  <si>
+    <t>ic1225@ic.ac.uk</t>
+  </si>
+  <si>
+    <t>mk3224@ic.ac.uk</t>
+  </si>
+  <si>
+    <t>zoraleshq@gmail.com</t>
+  </si>
+  <si>
+    <t>yyi25@ic.ac.uk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,6 +571,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -829,7 +877,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -872,11 +920,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -910,6 +960,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -933,10 +984,17 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Fazeel, Hakam" id="{A67B96EE-BB49-44FD-B492-CA70463271E6}" userId="S::hm1425@ic.ac.uk::4c7cae61-06ac-4978-ae34-bb31ef5291e4" providerId="AD"/>
+  <person displayName="Saeed, Javeria" id="{25F4D7F9-F80A-4593-8C0E-CB959BCA03BB}" userId="S::js4625@ic.ac.uk::1a756e2a-bec9-495e-9768-84afa6323d42" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -974,7 +1032,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1080,7 +1138,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1222,25 +1280,41 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B13" dT="2026-09-27T15:02:33.17" personId="{25F4D7F9-F80A-4593-8C0E-CB959BCA03BB}" id="{E59F53BC-32D6-4656-80B0-48EDCC40972B}">
+    <text>whos this?
+cant see them on mentee list</text>
+  </threadedComment>
+  <threadedComment ref="B13" dT="2026-09-28T12:15:35.98" personId="{A67B96EE-BB49-44FD-B492-CA70463271E6}" id="{E4B56FD2-2EDD-4C4B-B964-BF3143C95638}" parentId="{E59F53BC-32D6-4656-80B0-48EDCC40972B}">
+    <text>Some girl called Insia Zafar. Applying for materials. Shes on the mentee list</text>
+  </threadedComment>
+  <threadedComment ref="A50" dT="2026-09-27T15:03:02.68" personId="{25F4D7F9-F80A-4593-8C0E-CB959BCA03BB}" id="{350E727E-3F65-4A3F-8B56-638D0C8379BF}" done="1">
+    <text xml:space="preserve">manually added this sister (she didnt fill the form)
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC89125-2935-4BF9-9B18-8CED80E53B7B}">
-  <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC89125-2935-4BF9-9B18-8CED80E53B7B}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.140625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" customWidth="1"/>
     <col min="4" max="4" width="39.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1271,437 +1345,462 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>42</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>45</v>
       </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" t="s">
         <v>56</v>
       </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
+      <c r="D51" t="s">
         <v>67</v>
       </c>
-      <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" t="s">
-        <v>96</v>
-      </c>
-      <c r="B43" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" t="s">
-        <v>102</v>
-      </c>
-      <c r="E44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" t="s">
-        <v>105</v>
-      </c>
-      <c r="C45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" t="s">
-        <v>112</v>
-      </c>
-      <c r="B48" t="s">
-        <v>113</v>
-      </c>
-      <c r="C48" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>116</v>
-      </c>
-      <c r="B49" t="s">
-        <v>117</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A50" r:id="rId1" xr:uid="{6730C48A-E219-48B1-9C28-5C518C39A906}"/>
+    <hyperlink ref="A51" r:id="rId2" xr:uid="{7AEE81DA-C15C-48C3-A466-144C8DAF7642}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{1B38FEE4-6AAA-42F1-832F-DBE9B8230E82}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>